--- a/display/ToF_v1.xlsx
+++ b/display/ToF_v1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ToF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ToF" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD168"/>
+  <dimension ref="A1:AD181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -761,6 +761,11 @@
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -770,30 +775,55 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
+          <t>Payer</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
           <t>Continue Take-Up</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Cash-Out Stage</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Runs per Active Day</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Max Continues per Run</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Coin Balance override</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Top-Ups per Run</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Top-Up Take-Up</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Coin Bag Size</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Top-Ups per Season</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>What this row says about this player type</t>
         </is>
@@ -805,20 +835,37 @@
           <t>0-9</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>NONPAYER</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
         <v>0.05</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="D17" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="E17" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="11" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="F17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="11" t="inlineStr"/>
+      <c r="H17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>Rarely pays to revive, banks early at the first safe node.</t>
         </is>
@@ -827,1865 +874,921 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>10-19</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="D18" s="10" t="n">
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>PAYER</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="11" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Occasionally revives, pushes one safe node further.</t>
+      <c r="F18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="11" t="inlineStr"/>
+      <c r="H18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>Buys the odd small coin bag, but the ladder outruns them quickly.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>20-39</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="D19" s="10" t="n">
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>NONPAYER</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="11" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Revives one time in five, comfortable going past the halfway safe node.</t>
+      <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="11" t="inlineStr"/>
+      <c r="H19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>Occasionally revives, pushes one safe node further.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>40-99</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D20" s="10" t="n">
+          <t>10-19</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>PAYER</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="11" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Often revives, pushes deep because the coins are affordable.</t>
+      <c r="F20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="11" t="inlineStr"/>
+      <c r="H20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>Will buy a bag to save a run that is already going well.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>100+</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="D21" s="10" t="n">
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>NONPAYER</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E21" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="11" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Revives more often than not, so the Pig rarely stops the run.</t>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="11" t="inlineStr"/>
+      <c r="H21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>Revives one time in five, comfortable going past the halfway safe node.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>20-39</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>PAYER</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="11" t="inlineStr"/>
+      <c r="H22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Buys twice a run and pushes one node deeper than their non-paying twin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>NONPAYER</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="11" t="inlineStr"/>
+      <c r="H23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>Often revives, pushes deep because the coins are affordable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>40-99</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>PAYER</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="11" t="inlineStr"/>
+      <c r="H24" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Reliably tops up; the bag remainder carries into later continues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>NONPAYER</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="11" t="inlineStr"/>
+      <c r="H25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>Revives more often than not, so the Pig rarely stops the run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>PAYER</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="11" t="inlineStr"/>
+      <c r="H26" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>Tops up three times a run with the biggest bag, and banks deepest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
           <t>MAX</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>PAYER</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="10" t="n">
+      <c r="D27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="11" t="n">
+      <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="11" t="n">
         <v>100000</v>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="H27" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>999</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>CEILING CASE, not a real player: always revives, never banks early, and holds enough coins that price never stops them. Shows what the deep ladder is worth to someone who actually reaches it.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Continue Take-Up: the chance this player PAYS COINS to revive when a Pig ends their run. It is not a retention number. At 100% the Pig never stops them and every run reaches the end.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Cash-Out Stage: the node where this player voluntarily stops and banks what they have. They only get paid if they actually REACH it, because a Pig before then loses everything.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Runs per Active Day: a CAP, not the driver. Tickets are EARNED, so the engine walks the calendar day by day, banks whatever ToF_Ticket the other sources paid, and spends up to this many runs. Unspent tickets carry forward with no cap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Max Continues per Run: 0 means "as many as the CONTINUE COST LADDER has rungs" - the ladder length is the real cap, because a rung with no price cannot be sold. A number here lowers it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Coin Balance override: normally BLANK, and the sim reads the four hc_balance percentiles (p25/p50/p75/p90) for this segment straight from data_econ, walking the run at each and averaging. A number here replaces all four for this segment - which is how MAX gets a wallet no real player has.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTINUE COST LADDER</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>What it is: the COIN PRICE of reviving after a Pig, within a single run. The first revive in a run costs row 1, the second costs row 2, and so on. Costs must rise each time (deck p8).</t>
+          <t>Runs per Active Day: a CAP, not the driver. Tickets are EARNED, so the engine walks the calendar day by day, banks whatever ToF_Ticket the other sources paid, and spends up to this many runs. Unspent tickets carry forward with no cap.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>This is an INPUT you author. It is a coin SINK, the only one this event has, and it is how the feature is meant to make money.</t>
+          <t>Max Continues per Run: 0 means "as many as the CONTINUE COST LADDER has rungs" - the ladder length is the real cap, because a rung with no price cannot be sold. A number here lowers it.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
+          <t>Coin Balance override: normally BLANK, and the sim reads the four hc_balance percentiles (p25/p50/p75/p90) for this segment straight from data_econ, walking the run at each and averaging. A number here replaces all four for this segment - which is how MAX gets a wallet no real player has. NOTE: payers hold LESS coin than non-payers at every percentile of every segment (40-99: 0.26x at p90), because a balance is a STOCK and payers spend theirs. That is why the payer advantage is modelled as a purchase FLOW below, not as a bigger wallet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>THE FOUR TOP-UP COLUMNS (D53). Together they replace TOF_PAYER_TOPUPS, which was one hardcoded 1 in EcoGainsSim_v4.gs and the ONLY thing that made a payer different from a non-payer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Top-Ups per Run: how many times this player will buy coins inside ONE run. 0 = never, which is every non-payer row and is exactly the pre-D53 behaviour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Top-Up Take-Up: the chance they actually buy AT THE MOMENT the run would otherwise end - i.e. a Pig has come up, they want to continue, and the wallet cannot cover the price. It is not a conversion rate for the game; it is a willingness at one specific prompt. ASSUMPTION, not a measurement: no data source here separates a coin purchase made during this event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Coin Bag Size: the coins added by one purchase. NOT the price of the continue - a bag that overshoots leaves the REMAINDER in the wallet, and that remainder is what makes a payer progressively deeper rather than one rung better. Size it against the CONTINUE COST LADDER below, not in round numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Top-Ups per Season: the cap across the whole 33-day window. Without it a player buying twice a run over ~12 runs makes 24 purchases, which would make this event the biggest coin faucet in the game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>TO MAKE THIS BLOCK INERT (reproduce the pre-D53 numbers exactly): set Top-Up Take-Up to 0 on every row, and copy the Continue Take-Up and Cash-Out Stage of each PAYER row from the NONPAYER row above it. The engine then reads eleven rows that behave like the old six.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUE COST LADDER</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>What it is: the COIN PRICE of reviving after a Pig, within a single run. The first revive in a run costs row 1, the second costs row 2, and so on. Costs must rise each time (deck p8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>This is an INPUT you author. It is a coin SINK, the only one this event has, and it is how the feature is meant to make money.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
           <t>The first four rungs are priced against real wallets (data_econ hc_balance): rung 1 sits under every segment p25 so the first continue always feels affordable, and rungs 2-4 sit at the p50, p75 and p90 cumulative. Rung 5 onward is where the population has run out.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Growth multiplier and "growth stops after rung" are INPUTS. The cap is a rung INDEX rather than a price, so changing the multiplier moves the ceiling with it and no new cap has to be invented. Rungs past the cap repeat the capped price - a revive never gets more expensive than the cap, it just stays there.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Growth multiplier (rung 5+)</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B47" s="12" t="n">
         <v>2.5</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>Growth stops after rung #</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B48" s="6" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Continue # in this run</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Cost (Coins)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Cumulative if they revive this many times</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="n">
+    <row r="51">
+      <c r="A51" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B51" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="C38" s="13">
-        <f>SUM($B$38:$B38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="n">
+      <c r="C51" s="13">
+        <f>SUM($B$51:$B51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B52" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="C39" s="13">
-        <f>SUM($B$38:$B39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="n">
+      <c r="C52" s="13">
+        <f>SUM($B$51:$B52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B53" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="C40" s="13">
-        <f>SUM($B$38:$B40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B41" s="6" t="n">
-        <v>460</v>
-      </c>
-      <c r="C41" s="13">
-        <f>SUM($B$38:$B41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B42" s="13">
-        <f>ROUND($B$41*$B$34^MAX(0,MIN($A42-4,$B$35-4)),0)</f>
-        <v/>
-      </c>
-      <c r="C42" s="13">
-        <f>SUM($B$38:$B42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B43" s="13">
-        <f>ROUND($B$41*$B$34^MAX(0,MIN($A43-4,$B$35-4)),0)</f>
-        <v/>
-      </c>
-      <c r="C43" s="13">
-        <f>SUM($B$38:$B43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B44" s="13">
-        <f>ROUND($B$41*$B$34^MAX(0,MIN($A44-4,$B$35-4)),0)</f>
-        <v/>
-      </c>
-      <c r="C44" s="13">
-        <f>SUM($B$38:$B44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B45" s="13">
-        <f>ROUND($B$41*$B$34^MAX(0,MIN($A45-4,$B$35-4)),0)</f>
-        <v/>
-      </c>
-      <c r="C45" s="13">
-        <f>SUM($B$38:$B45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B46" s="13">
-        <f>ROUND($B$41*$B$34^MAX(0,MIN($A46-4,$B$35-4)),0)</f>
-        <v/>
-      </c>
-      <c r="C46" s="13">
-        <f>SUM($B$38:$B46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B47" s="13">
-        <f>ROUND($B$41*$B$34^MAX(0,MIN($A47-4,$B$35-4)),0)</f>
-        <v/>
-      </c>
-      <c r="C47" s="13">
-        <f>SUM($B$38:$B47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>STAGES</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="3" t="n"/>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
-      <c r="J49" s="3" t="n"/>
-      <c r="K49" s="3" t="n"/>
-      <c r="L49" s="3" t="n"/>
-      <c r="M49" s="3" t="n"/>
-      <c r="N49" s="3" t="n"/>
-      <c r="O49" s="3" t="n"/>
-      <c r="P49" s="3" t="n"/>
-      <c r="Q49" s="3" t="n"/>
-      <c r="R49" s="3" t="n"/>
-      <c r="S49" s="3" t="n"/>
-      <c r="T49" s="3" t="n"/>
-      <c r="U49" s="3" t="n"/>
-      <c r="V49" s="3" t="n"/>
-      <c r="W49" s="3" t="n"/>
-      <c r="X49" s="3" t="n"/>
-      <c r="Y49" s="3" t="n"/>
-      <c r="Z49" s="3" t="n"/>
-      <c r="AA49" s="3" t="n"/>
-      <c r="AB49" s="3" t="n"/>
-      <c r="AC49" s="3" t="n"/>
-      <c r="AD49" s="3" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>One row per node. Pig Slots rises with depth (1 for stages 1 to 20, 2 for 21 to 40, 3 for 41 to 60) and never goes above 3, so later nodes are far more dangerous. Safe nodes carry none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>Which door hides the Pig is drawn at random when the player arrives, so only the COUNT is configurable, never the position.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>Rewards are tuned so the event pays each segment roughly 75% of what Rainbow Maker pays, allowing for 3 days against Rainbow Maker 4. See builders/_md_ladder.py for the solve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Reward Slots</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>Pig Slots</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>Empty Slots</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>Survive p</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>P(reward | survived)</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>Coins</t>
-        </is>
-      </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>SPT</t>
-        </is>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>SPT x2</t>
-        </is>
-      </c>
-      <c r="M53" s="4" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="N53" s="4" t="inlineStr">
-        <is>
-          <t>Chuck</t>
-        </is>
-      </c>
-      <c r="O53" s="4" t="inlineStr">
-        <is>
-          <t>Bomb</t>
-        </is>
-      </c>
-      <c r="P53" s="4" t="inlineStr">
-        <is>
-          <t>Slingshot</t>
-        </is>
-      </c>
-      <c r="Q53" s="4" t="inlineStr">
-        <is>
-          <t>Shuffle</t>
-        </is>
-      </c>
-      <c r="R53" s="4" t="inlineStr">
-        <is>
-          <t>Comet</t>
-        </is>
-      </c>
-      <c r="S53" s="4" t="inlineStr">
-        <is>
-          <t>Unlimited Lives</t>
-        </is>
-      </c>
-      <c r="T53" s="4" t="inlineStr">
-        <is>
-          <t>Unlimited Red</t>
-        </is>
-      </c>
-      <c r="U53" s="4" t="inlineStr">
-        <is>
-          <t>Unlimited Chuck</t>
-        </is>
-      </c>
-      <c r="V53" s="4" t="inlineStr">
-        <is>
-          <t>Unlimited Bomb</t>
-        </is>
-      </c>
-      <c r="W53" s="4" t="inlineStr">
-        <is>
-          <t>COOP Token</t>
-        </is>
-      </c>
-      <c r="X53" s="4" t="inlineStr">
-        <is>
-          <t>Avatar</t>
-        </is>
-      </c>
-      <c r="Y53" s="4" t="inlineStr">
-        <is>
-          <t>1-star Dly</t>
-        </is>
-      </c>
-      <c r="Z53" s="4" t="inlineStr">
-        <is>
-          <t>2-star Dly</t>
-        </is>
-      </c>
-      <c r="AA53" s="4" t="inlineStr">
-        <is>
-          <t>3-star Dly</t>
-        </is>
-      </c>
-      <c r="AB53" s="4" t="inlineStr">
-        <is>
-          <t>4-star Dly</t>
-        </is>
-      </c>
-      <c r="AC53" s="4" t="inlineStr">
-        <is>
-          <t>5-star Dly</t>
-        </is>
-      </c>
-      <c r="AD53" s="4" t="inlineStr">
-        <is>
-          <t>6-star Dly</t>
-        </is>
+      <c r="C53" s="13">
+        <f>SUM($B$51:$B53)</f>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B54" s="14">
-        <f>IF(A54=1,"Safe (Start)",IF(OR(A54=$B$8,A54=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A54,$B$7)=0),"Safe","Standard")))</f>
-        <v/>
-      </c>
-      <c r="C54" s="14">
-        <f>MIN(6,MAX(1,ROUNDUP(A54/$B$10,0)))</f>
-        <v/>
-      </c>
-      <c r="D54" s="6">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="E54" s="14">
-        <f>MAX(0,$D54-$F54-$G54)</f>
-        <v/>
-      </c>
-      <c r="F54" s="14">
-        <f>IF($B54&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C54&lt;=2,1,IF($C54&lt;=4,2,3)))))</f>
-        <v/>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="15">
-        <f>IF($D54&lt;=0,0,($D54-$F54)/$D54)</f>
-        <v/>
-      </c>
-      <c r="I54" s="15">
-        <f>IF($D54-$F54&lt;=0,0,$E54/($D54-$F54))</f>
-        <v/>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>460</v>
+      </c>
+      <c r="C54" s="13">
+        <f>SUM($B$51:$B54)</f>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B55" s="14">
-        <f>IF(A55=1,"Safe (Start)",IF(OR(A55=$B$8,A55=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A55,$B$7)=0),"Safe","Standard")))</f>
-        <v/>
-      </c>
-      <c r="C55" s="14">
-        <f>MIN(6,MAX(1,ROUNDUP(A55/$B$10,0)))</f>
-        <v/>
-      </c>
-      <c r="D55" s="6">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="E55" s="14">
-        <f>MAX(0,$D55-$F55-$G55)</f>
-        <v/>
-      </c>
-      <c r="F55" s="14">
-        <f>IF($B55&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C55&lt;=2,1,IF($C55&lt;=4,2,3)))))</f>
-        <v/>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="15">
-        <f>IF($D55&lt;=0,0,($D55-$F55)/$D55)</f>
-        <v/>
-      </c>
-      <c r="I55" s="15">
-        <f>IF($D55-$F55&lt;=0,0,$E55/($D55-$F55))</f>
-        <v/>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="B55" s="13">
+        <f>ROUND($B$54*$B$47^MAX(0,MIN($A55-4,$B$48-4)),0)</f>
+        <v/>
+      </c>
+      <c r="C55" s="13">
+        <f>SUM($B$51:$B55)</f>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B56" s="14">
-        <f>IF(A56=1,"Safe (Start)",IF(OR(A56=$B$8,A56=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A56,$B$7)=0),"Safe","Standard")))</f>
-        <v/>
-      </c>
-      <c r="C56" s="14">
-        <f>MIN(6,MAX(1,ROUNDUP(A56/$B$10,0)))</f>
-        <v/>
-      </c>
-      <c r="D56" s="6">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="E56" s="14">
-        <f>MAX(0,$D56-$F56-$G56)</f>
-        <v/>
-      </c>
-      <c r="F56" s="14">
-        <f>IF($B56&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C56&lt;=2,1,IF($C56&lt;=4,2,3)))))</f>
-        <v/>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="15">
-        <f>IF($D56&lt;=0,0,($D56-$F56)/$D56)</f>
-        <v/>
-      </c>
-      <c r="I56" s="15">
-        <f>IF($D56-$F56&lt;=0,0,$E56/($D56-$F56))</f>
-        <v/>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="B56" s="13">
+        <f>ROUND($B$54*$B$47^MAX(0,MIN($A56-4,$B$48-4)),0)</f>
+        <v/>
+      </c>
+      <c r="C56" s="13">
+        <f>SUM($B$51:$B56)</f>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B57" s="14">
-        <f>IF(A57=1,"Safe (Start)",IF(OR(A57=$B$8,A57=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A57,$B$7)=0),"Safe","Standard")))</f>
-        <v/>
-      </c>
-      <c r="C57" s="14">
-        <f>MIN(6,MAX(1,ROUNDUP(A57/$B$10,0)))</f>
-        <v/>
-      </c>
-      <c r="D57" s="6">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="E57" s="14">
-        <f>MAX(0,$D57-$F57-$G57)</f>
-        <v/>
-      </c>
-      <c r="F57" s="14">
-        <f>IF($B57&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C57&lt;=2,1,IF($C57&lt;=4,2,3)))))</f>
-        <v/>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="15">
-        <f>IF($D57&lt;=0,0,($D57-$F57)/$D57)</f>
-        <v/>
-      </c>
-      <c r="I57" s="15">
-        <f>IF($D57-$F57&lt;=0,0,$E57/($D57-$F57))</f>
-        <v/>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="B57" s="13">
+        <f>ROUND($B$54*$B$47^MAX(0,MIN($A57-4,$B$48-4)),0)</f>
+        <v/>
+      </c>
+      <c r="C57" s="13">
+        <f>SUM($B$51:$B57)</f>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B58" s="14">
-        <f>IF(A58=1,"Safe (Start)",IF(OR(A58=$B$8,A58=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A58,$B$7)=0),"Safe","Standard")))</f>
-        <v/>
-      </c>
-      <c r="C58" s="14">
-        <f>MIN(6,MAX(1,ROUNDUP(A58/$B$10,0)))</f>
-        <v/>
-      </c>
-      <c r="D58" s="6">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="E58" s="14">
-        <f>MAX(0,$D58-$F58-$G58)</f>
-        <v/>
-      </c>
-      <c r="F58" s="14">
-        <f>IF($B58&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C58&lt;=2,1,IF($C58&lt;=4,2,3)))))</f>
-        <v/>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="15">
-        <f>IF($D58&lt;=0,0,($D58-$F58)/$D58)</f>
-        <v/>
-      </c>
-      <c r="I58" s="15">
-        <f>IF($D58-$F58&lt;=0,0,$E58/($D58-$F58))</f>
-        <v/>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="B58" s="13">
+        <f>ROUND($B$54*$B$47^MAX(0,MIN($A58-4,$B$48-4)),0)</f>
+        <v/>
+      </c>
+      <c r="C58" s="13">
+        <f>SUM($B$51:$B58)</f>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B59" s="14">
-        <f>IF(A59=1,"Safe (Start)",IF(OR(A59=$B$8,A59=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A59,$B$7)=0),"Safe","Standard")))</f>
-        <v/>
-      </c>
-      <c r="C59" s="14">
-        <f>MIN(6,MAX(1,ROUNDUP(A59/$B$10,0)))</f>
-        <v/>
-      </c>
-      <c r="D59" s="6">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="E59" s="14">
-        <f>MAX(0,$D59-$F59-$G59)</f>
-        <v/>
-      </c>
-      <c r="F59" s="14">
-        <f>IF($B59&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C59&lt;=2,1,IF($C59&lt;=4,2,3)))))</f>
-        <v/>
-      </c>
-      <c r="G59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="15">
-        <f>IF($D59&lt;=0,0,($D59-$F59)/$D59)</f>
-        <v/>
-      </c>
-      <c r="I59" s="15">
-        <f>IF($D59-$F59&lt;=0,0,$E59/($D59-$F59))</f>
-        <v/>
-      </c>
-      <c r="J59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="B59" s="13">
+        <f>ROUND($B$54*$B$47^MAX(0,MIN($A59-4,$B$48-4)),0)</f>
+        <v/>
+      </c>
+      <c r="C59" s="13">
+        <f>SUM($B$51:$B59)</f>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B60" s="14">
-        <f>IF(A60=1,"Safe (Start)",IF(OR(A60=$B$8,A60=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A60,$B$7)=0),"Safe","Standard")))</f>
-        <v/>
-      </c>
-      <c r="C60" s="14">
-        <f>MIN(6,MAX(1,ROUNDUP(A60/$B$10,0)))</f>
-        <v/>
-      </c>
-      <c r="D60" s="6">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="E60" s="14">
-        <f>MAX(0,$D60-$F60-$G60)</f>
-        <v/>
-      </c>
-      <c r="F60" s="14">
-        <f>IF($B60&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C60&lt;=2,1,IF($C60&lt;=4,2,3)))))</f>
-        <v/>
-      </c>
-      <c r="G60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="15">
-        <f>IF($D60&lt;=0,0,($D60-$F60)/$D60)</f>
-        <v/>
-      </c>
-      <c r="I60" s="15">
-        <f>IF($D60-$F60&lt;=0,0,$E60/($D60-$F60))</f>
-        <v/>
-      </c>
-      <c r="J60" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K60" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="L60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B61" s="14">
-        <f>IF(A61=1,"Safe (Start)",IF(OR(A61=$B$8,A61=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A61,$B$7)=0),"Safe","Standard")))</f>
-        <v/>
-      </c>
-      <c r="C61" s="14">
-        <f>MIN(6,MAX(1,ROUNDUP(A61/$B$10,0)))</f>
-        <v/>
-      </c>
-      <c r="D61" s="6">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="E61" s="14">
-        <f>MAX(0,$D61-$F61-$G61)</f>
-        <v/>
-      </c>
-      <c r="F61" s="14">
-        <f>IF($B61&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C61&lt;=2,1,IF($C61&lt;=4,2,3)))))</f>
-        <v/>
-      </c>
-      <c r="G61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="15">
-        <f>IF($D61&lt;=0,0,($D61-$F61)/$D61)</f>
-        <v/>
-      </c>
-      <c r="I61" s="15">
-        <f>IF($D61-$F61&lt;=0,0,$E61/($D61-$F61))</f>
-        <v/>
-      </c>
-      <c r="J61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="L61" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="T61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="6" t="n">
-        <v>0</v>
+      <c r="B60" s="13">
+        <f>ROUND($B$54*$B$47^MAX(0,MIN($A60-4,$B$48-4)),0)</f>
+        <v/>
+      </c>
+      <c r="C60" s="13">
+        <f>SUM($B$51:$B60)</f>
+        <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B62" s="14">
-        <f>IF(A62=1,"Safe (Start)",IF(OR(A62=$B$8,A62=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A62,$B$7)=0),"Safe","Standard")))</f>
-        <v/>
-      </c>
-      <c r="C62" s="14">
-        <f>MIN(6,MAX(1,ROUNDUP(A62/$B$10,0)))</f>
-        <v/>
-      </c>
-      <c r="D62" s="6">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="E62" s="14">
-        <f>MAX(0,$D62-$F62-$G62)</f>
-        <v/>
-      </c>
-      <c r="F62" s="14">
-        <f>IF($B62&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C62&lt;=2,1,IF($C62&lt;=4,2,3)))))</f>
-        <v/>
-      </c>
-      <c r="G62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="15">
-        <f>IF($D62&lt;=0,0,($D62-$F62)/$D62)</f>
-        <v/>
-      </c>
-      <c r="I62" s="15">
-        <f>IF($D62-$F62&lt;=0,0,$E62/($D62-$F62))</f>
-        <v/>
-      </c>
-      <c r="J62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="L62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>STAGES</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+      <c r="I62" s="3" t="n"/>
+      <c r="J62" s="3" t="n"/>
+      <c r="K62" s="3" t="n"/>
+      <c r="L62" s="3" t="n"/>
+      <c r="M62" s="3" t="n"/>
+      <c r="N62" s="3" t="n"/>
+      <c r="O62" s="3" t="n"/>
+      <c r="P62" s="3" t="n"/>
+      <c r="Q62" s="3" t="n"/>
+      <c r="R62" s="3" t="n"/>
+      <c r="S62" s="3" t="n"/>
+      <c r="T62" s="3" t="n"/>
+      <c r="U62" s="3" t="n"/>
+      <c r="V62" s="3" t="n"/>
+      <c r="W62" s="3" t="n"/>
+      <c r="X62" s="3" t="n"/>
+      <c r="Y62" s="3" t="n"/>
+      <c r="Z62" s="3" t="n"/>
+      <c r="AA62" s="3" t="n"/>
+      <c r="AB62" s="3" t="n"/>
+      <c r="AC62" s="3" t="n"/>
+      <c r="AD62" s="3" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B63" s="14">
-        <f>IF(A63=1,"Safe (Start)",IF(OR(A63=$B$8,A63=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A63,$B$7)=0),"Safe","Standard")))</f>
-        <v/>
-      </c>
-      <c r="C63" s="14">
-        <f>MIN(6,MAX(1,ROUNDUP(A63/$B$10,0)))</f>
-        <v/>
-      </c>
-      <c r="D63" s="6">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="E63" s="14">
-        <f>MAX(0,$D63-$F63-$G63)</f>
-        <v/>
-      </c>
-      <c r="F63" s="14">
-        <f>IF($B63&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C63&lt;=2,1,IF($C63&lt;=4,2,3)))))</f>
-        <v/>
-      </c>
-      <c r="G63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="15">
-        <f>IF($D63&lt;=0,0,($D63-$F63)/$D63)</f>
-        <v/>
-      </c>
-      <c r="I63" s="15">
-        <f>IF($D63-$F63&lt;=0,0,$E63/($D63-$F63))</f>
-        <v/>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K63" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="L63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD63" s="6" t="n">
-        <v>0</v>
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>One row per node. Pig Slots rises with depth (1 for stages 1 to 20, 2 for 21 to 40, 3 for 41 to 60) and never goes above 3, so later nodes are far more dangerous. Safe nodes carry none.</t>
+        </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B64" s="14">
-        <f>IF(A64=1,"Safe (Start)",IF(OR(A64=$B$8,A64=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A64,$B$7)=0),"Safe","Standard")))</f>
-        <v/>
-      </c>
-      <c r="C64" s="14">
-        <f>MIN(6,MAX(1,ROUNDUP(A64/$B$10,0)))</f>
-        <v/>
-      </c>
-      <c r="D64" s="6">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="E64" s="14">
-        <f>MAX(0,$D64-$F64-$G64)</f>
-        <v/>
-      </c>
-      <c r="F64" s="14">
-        <f>IF($B64&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C64&lt;=2,1,IF($C64&lt;=4,2,3)))))</f>
-        <v/>
-      </c>
-      <c r="G64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="15">
-        <f>IF($D64&lt;=0,0,($D64-$F64)/$D64)</f>
-        <v/>
-      </c>
-      <c r="I64" s="15">
-        <f>IF($D64-$F64&lt;=0,0,$E64/($D64-$F64))</f>
-        <v/>
-      </c>
-      <c r="J64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="L64" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD64" s="6" t="n">
-        <v>0</v>
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Which door hides the Pig is drawn at random when the player arrives, so only the COUNT is configurable, never the position.</t>
+        </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B65" s="14">
-        <f>IF(A65=1,"Safe (Start)",IF(OR(A65=$B$8,A65=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A65,$B$7)=0),"Safe","Standard")))</f>
-        <v/>
-      </c>
-      <c r="C65" s="14">
-        <f>MIN(6,MAX(1,ROUNDUP(A65/$B$10,0)))</f>
-        <v/>
-      </c>
-      <c r="D65" s="6">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="E65" s="14">
-        <f>MAX(0,$D65-$F65-$G65)</f>
-        <v/>
-      </c>
-      <c r="F65" s="14">
-        <f>IF($B65&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C65&lt;=2,1,IF($C65&lt;=4,2,3)))))</f>
-        <v/>
-      </c>
-      <c r="G65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="15">
-        <f>IF($D65&lt;=0,0,($D65-$F65)/$D65)</f>
-        <v/>
-      </c>
-      <c r="I65" s="15">
-        <f>IF($D65-$F65&lt;=0,0,$E65/($D65-$F65))</f>
-        <v/>
-      </c>
-      <c r="J65" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K65" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="L65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD65" s="6" t="n">
-        <v>0</v>
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Rewards are tuned so the event pays each segment roughly 75% of what Rainbow Maker pays, allowing for 3 days against Rainbow Maker 4. See builders/_md_ladder.py for the solve.</t>
+        </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B66" s="14">
-        <f>IF(A66=1,"Safe (Start)",IF(OR(A66=$B$8,A66=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A66,$B$7)=0),"Safe","Standard")))</f>
-        <v/>
-      </c>
-      <c r="C66" s="14">
-        <f>MIN(6,MAX(1,ROUNDUP(A66/$B$10,0)))</f>
-        <v/>
-      </c>
-      <c r="D66" s="6">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="E66" s="14">
-        <f>MAX(0,$D66-$F66-$G66)</f>
-        <v/>
-      </c>
-      <c r="F66" s="14">
-        <f>IF($B66&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C66&lt;=2,1,IF($C66&lt;=4,2,3)))))</f>
-        <v/>
-      </c>
-      <c r="G66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="15">
-        <f>IF($D66&lt;=0,0,($D66-$F66)/$D66)</f>
-        <v/>
-      </c>
-      <c r="I66" s="15">
-        <f>IF($D66-$F66&lt;=0,0,$E66/($D66-$F66))</f>
-        <v/>
-      </c>
-      <c r="J66" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K66" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="L66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD66" s="6" t="n">
-        <v>0</v>
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Reward Slots</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Pig Slots</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Empty Slots</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Survive p</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>P(reward | survived)</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>Coins</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>SPT x2</t>
+        </is>
+      </c>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>Chuck</t>
+        </is>
+      </c>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>Bomb</t>
+        </is>
+      </c>
+      <c r="P66" s="4" t="inlineStr">
+        <is>
+          <t>Slingshot</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="inlineStr">
+        <is>
+          <t>Shuffle</t>
+        </is>
+      </c>
+      <c r="R66" s="4" t="inlineStr">
+        <is>
+          <t>Comet</t>
+        </is>
+      </c>
+      <c r="S66" s="4" t="inlineStr">
+        <is>
+          <t>Unlimited Lives</t>
+        </is>
+      </c>
+      <c r="T66" s="4" t="inlineStr">
+        <is>
+          <t>Unlimited Red</t>
+        </is>
+      </c>
+      <c r="U66" s="4" t="inlineStr">
+        <is>
+          <t>Unlimited Chuck</t>
+        </is>
+      </c>
+      <c r="V66" s="4" t="inlineStr">
+        <is>
+          <t>Unlimited Bomb</t>
+        </is>
+      </c>
+      <c r="W66" s="4" t="inlineStr">
+        <is>
+          <t>COOP Token</t>
+        </is>
+      </c>
+      <c r="X66" s="4" t="inlineStr">
+        <is>
+          <t>Avatar</t>
+        </is>
+      </c>
+      <c r="Y66" s="4" t="inlineStr">
+        <is>
+          <t>1-star Dly</t>
+        </is>
+      </c>
+      <c r="Z66" s="4" t="inlineStr">
+        <is>
+          <t>2-star Dly</t>
+        </is>
+      </c>
+      <c r="AA66" s="4" t="inlineStr">
+        <is>
+          <t>3-star Dly</t>
+        </is>
+      </c>
+      <c r="AB66" s="4" t="inlineStr">
+        <is>
+          <t>4-star Dly</t>
+        </is>
+      </c>
+      <c r="AC66" s="4" t="inlineStr">
+        <is>
+          <t>5-star Dly</t>
+        </is>
+      </c>
+      <c r="AD66" s="4" t="inlineStr">
+        <is>
+          <t>6-star Dly</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B67" s="14">
         <f>IF(A67=1,"Safe (Start)",IF(OR(A67=$B$8,A67=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A67,$B$7)=0),"Safe","Standard")))</f>
@@ -2722,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="L67" s="6" t="n">
         <v>0</v>
@@ -2784,7 +1887,7 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B68" s="14">
         <f>IF(A68=1,"Safe (Start)",IF(OR(A68=$B$8,A68=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A68,$B$7)=0),"Safe","Standard")))</f>
@@ -2818,13 +1921,13 @@
         <v/>
       </c>
       <c r="J68" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="6" t="n">
         <v>0</v>
@@ -2836,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="P68" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q68" s="6" t="n">
         <v>0</v>
@@ -2845,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="S68" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T68" s="6" t="n">
         <v>0</v>
@@ -2863,10 +1966,10 @@
         <v>0</v>
       </c>
       <c r="Y68" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z68" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA68" s="6" t="n">
         <v>0</v>
@@ -2883,7 +1986,7 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B69" s="14">
         <f>IF(A69=1,"Safe (Start)",IF(OR(A69=$B$8,A69=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A69,$B$7)=0),"Safe","Standard")))</f>
@@ -2917,10 +2020,10 @@
         <v/>
       </c>
       <c r="J69" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L69" s="6" t="n">
         <v>0</v>
@@ -2982,7 +2085,7 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B70" s="14">
         <f>IF(A70=1,"Safe (Start)",IF(OR(A70=$B$8,A70=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A70,$B$7)=0),"Safe","Standard")))</f>
@@ -3016,10 +2119,10 @@
         <v/>
       </c>
       <c r="J70" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L70" s="6" t="n">
         <v>0</v>
@@ -3040,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="R70" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" s="6" t="n">
         <v>0</v>
@@ -3081,7 +2184,7 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B71" s="14">
         <f>IF(A71=1,"Safe (Start)",IF(OR(A71=$B$8,A71=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A71,$B$7)=0),"Safe","Standard")))</f>
@@ -3115,10 +2218,10 @@
         <v/>
       </c>
       <c r="J71" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L71" s="6" t="n">
         <v>0</v>
@@ -3180,7 +2283,7 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B72" s="14">
         <f>IF(A72=1,"Safe (Start)",IF(OR(A72=$B$8,A72=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A72,$B$7)=0),"Safe","Standard")))</f>
@@ -3217,7 +2320,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
@@ -3279,7 +2382,7 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B73" s="14">
         <f>IF(A73=1,"Safe (Start)",IF(OR(A73=$B$8,A73=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A73,$B$7)=0),"Safe","Standard")))</f>
@@ -3316,7 +2419,7 @@
         <v>5</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L73" s="6" t="n">
         <v>0</v>
@@ -3378,7 +2481,7 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B74" s="14">
         <f>IF(A74=1,"Safe (Start)",IF(OR(A74=$B$8,A74=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A74,$B$7)=0),"Safe","Standard")))</f>
@@ -3412,13 +2515,13 @@
         <v/>
       </c>
       <c r="J74" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="K74" s="6" t="n">
-        <v>12</v>
-      </c>
       <c r="L74" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="6" t="n">
         <v>0</v>
@@ -3427,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="O74" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P74" s="6" t="n">
         <v>0</v>
@@ -3439,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T74" s="6" t="n">
         <v>0</v>
@@ -3477,7 +2580,7 @@
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B75" s="14">
         <f>IF(A75=1,"Safe (Start)",IF(OR(A75=$B$8,A75=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A75,$B$7)=0),"Safe","Standard")))</f>
@@ -3511,10 +2614,10 @@
         <v/>
       </c>
       <c r="J75" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L75" s="6" t="n">
         <v>0</v>
@@ -3576,7 +2679,7 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B76" s="14">
         <f>IF(A76=1,"Safe (Start)",IF(OR(A76=$B$8,A76=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A76,$B$7)=0),"Safe","Standard")))</f>
@@ -3613,7 +2716,7 @@
         <v>5</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L76" s="6" t="n">
         <v>0</v>
@@ -3675,7 +2778,7 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B77" s="14">
         <f>IF(A77=1,"Safe (Start)",IF(OR(A77=$B$8,A77=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A77,$B$7)=0),"Safe","Standard")))</f>
@@ -3712,10 +2815,10 @@
         <v>0</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L77" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="6" t="n">
         <v>0</v>
@@ -3774,7 +2877,7 @@
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B78" s="14">
         <f>IF(A78=1,"Safe (Start)",IF(OR(A78=$B$8,A78=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A78,$B$7)=0),"Safe","Standard")))</f>
@@ -3808,16 +2911,16 @@
         <v/>
       </c>
       <c r="J78" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L78" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M78" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N78" s="6" t="n">
         <v>0</v>
@@ -3865,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="AC78" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD78" s="6" t="n">
         <v>0</v>
@@ -3873,7 +2976,7 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B79" s="14">
         <f>IF(A79=1,"Safe (Start)",IF(OR(A79=$B$8,A79=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A79,$B$7)=0),"Safe","Standard")))</f>
@@ -3910,7 +3013,7 @@
         <v>5</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L79" s="6" t="n">
         <v>0</v>
@@ -3972,7 +3075,7 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B80" s="14">
         <f>IF(A80=1,"Safe (Start)",IF(OR(A80=$B$8,A80=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A80,$B$7)=0),"Safe","Standard")))</f>
@@ -4006,10 +3109,10 @@
         <v/>
       </c>
       <c r="J80" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L80" s="6" t="n">
         <v>0</v>
@@ -4071,7 +3174,7 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B81" s="14">
         <f>IF(A81=1,"Safe (Start)",IF(OR(A81=$B$8,A81=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A81,$B$7)=0),"Safe","Standard")))</f>
@@ -4108,10 +3211,10 @@
         <v>5</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L81" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="6" t="n">
         <v>0</v>
@@ -4123,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="P81" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="6" t="n">
         <v>0</v>
@@ -4132,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="S81" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T81" s="6" t="n">
         <v>0</v>
@@ -4150,16 +3253,16 @@
         <v>0</v>
       </c>
       <c r="Y81" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z81" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA81" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AB81" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC81" s="6" t="n">
         <v>0</v>
@@ -4170,7 +3273,7 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B82" s="14">
         <f>IF(A82=1,"Safe (Start)",IF(OR(A82=$B$8,A82=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A82,$B$7)=0),"Safe","Standard")))</f>
@@ -4207,7 +3310,7 @@
         <v>5</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L82" s="6" t="n">
         <v>0</v>
@@ -4269,7 +3372,7 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B83" s="14">
         <f>IF(A83=1,"Safe (Start)",IF(OR(A83=$B$8,A83=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A83,$B$7)=0),"Safe","Standard")))</f>
@@ -4306,25 +3409,25 @@
         <v>5</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="L83" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M83" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N83" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O83" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P83" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R83" s="6" t="n">
         <v>1</v>
@@ -4336,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="U83" s="6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="V83" s="6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="W83" s="6" t="n">
         <v>0</v>
@@ -4348,13 +3451,13 @@
         <v>0</v>
       </c>
       <c r="Y83" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z83" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA83" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB83" s="6" t="n">
         <v>0</v>
@@ -4368,7 +3471,7 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B84" s="14">
         <f>IF(A84=1,"Safe (Start)",IF(OR(A84=$B$8,A84=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A84,$B$7)=0),"Safe","Standard")))</f>
@@ -4402,10 +3505,10 @@
         <v/>
       </c>
       <c r="J84" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L84" s="6" t="n">
         <v>0</v>
@@ -4467,7 +3570,7 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B85" s="14">
         <f>IF(A85=1,"Safe (Start)",IF(OR(A85=$B$8,A85=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A85,$B$7)=0),"Safe","Standard")))</f>
@@ -4501,10 +3604,10 @@
         <v/>
       </c>
       <c r="J85" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L85" s="6" t="n">
         <v>0</v>
@@ -4516,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="O85" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P85" s="6" t="n">
         <v>0</v>
@@ -4566,7 +3669,7 @@
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B86" s="14">
         <f>IF(A86=1,"Safe (Start)",IF(OR(A86=$B$8,A86=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A86,$B$7)=0),"Safe","Standard")))</f>
@@ -4603,7 +3706,7 @@
         <v>5</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="L86" s="6" t="n">
         <v>0</v>
@@ -4665,7 +3768,7 @@
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B87" s="14">
         <f>IF(A87=1,"Safe (Start)",IF(OR(A87=$B$8,A87=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A87,$B$7)=0),"Safe","Standard")))</f>
@@ -4702,7 +3805,7 @@
         <v>5</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="L87" s="6" t="n">
         <v>0</v>
@@ -4714,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="O87" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P87" s="6" t="n">
         <v>0</v>
@@ -4764,7 +3867,7 @@
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B88" s="14">
         <f>IF(A88=1,"Safe (Start)",IF(OR(A88=$B$8,A88=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A88,$B$7)=0),"Safe","Standard")))</f>
@@ -4798,10 +3901,10 @@
         <v/>
       </c>
       <c r="J88" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="L88" s="6" t="n">
         <v>0</v>
@@ -4863,7 +3966,7 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B89" s="14">
         <f>IF(A89=1,"Safe (Start)",IF(OR(A89=$B$8,A89=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A89,$B$7)=0),"Safe","Standard")))</f>
@@ -4897,10 +4000,10 @@
         <v/>
       </c>
       <c r="J89" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="L89" s="6" t="n">
         <v>0</v>
@@ -4918,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="Q89" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" s="6" t="n">
         <v>0</v>
@@ -4962,7 +4065,7 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B90" s="14">
         <f>IF(A90=1,"Safe (Start)",IF(OR(A90=$B$8,A90=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A90,$B$7)=0),"Safe","Standard")))</f>
@@ -4996,10 +4099,10 @@
         <v/>
       </c>
       <c r="J90" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L90" s="6" t="n">
         <v>0</v>
@@ -5061,7 +4164,7 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B91" s="14">
         <f>IF(A91=1,"Safe (Start)",IF(OR(A91=$B$8,A91=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A91,$B$7)=0),"Safe","Standard")))</f>
@@ -5098,7 +4201,7 @@
         <v>10</v>
       </c>
       <c r="K91" s="6" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L91" s="6" t="n">
         <v>0</v>
@@ -5160,7 +4263,7 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B92" s="14">
         <f>IF(A92=1,"Safe (Start)",IF(OR(A92=$B$8,A92=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A92,$B$7)=0),"Safe","Standard")))</f>
@@ -5197,7 +4300,7 @@
         <v>5</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>0</v>
@@ -5259,7 +4362,7 @@
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B93" s="14">
         <f>IF(A93=1,"Safe (Start)",IF(OR(A93=$B$8,A93=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A93,$B$7)=0),"Safe","Standard")))</f>
@@ -5293,10 +4396,10 @@
         <v/>
       </c>
       <c r="J93" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K93" s="6" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L93" s="6" t="n">
         <v>0</v>
@@ -5308,7 +4411,7 @@
         <v>0</v>
       </c>
       <c r="O93" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P93" s="6" t="n">
         <v>0</v>
@@ -5358,7 +4461,7 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B94" s="14">
         <f>IF(A94=1,"Safe (Start)",IF(OR(A94=$B$8,A94=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A94,$B$7)=0),"Safe","Standard")))</f>
@@ -5392,10 +4495,10 @@
         <v/>
       </c>
       <c r="J94" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L94" s="6" t="n">
         <v>0</v>
@@ -5446,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="AB94" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC94" s="6" t="n">
         <v>0</v>
@@ -5457,7 +4560,7 @@
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B95" s="14">
         <f>IF(A95=1,"Safe (Start)",IF(OR(A95=$B$8,A95=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A95,$B$7)=0),"Safe","Standard")))</f>
@@ -5494,7 +4597,7 @@
         <v>5</v>
       </c>
       <c r="K95" s="6" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="L95" s="6" t="n">
         <v>0</v>
@@ -5556,7 +4659,7 @@
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B96" s="14">
         <f>IF(A96=1,"Safe (Start)",IF(OR(A96=$B$8,A96=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A96,$B$7)=0),"Safe","Standard")))</f>
@@ -5590,31 +4693,31 @@
         <v/>
       </c>
       <c r="J96" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L96" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N96" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O96" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P96" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q96" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R96" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S96" s="6" t="n">
         <v>0</v>
@@ -5623,10 +4726,10 @@
         <v>0</v>
       </c>
       <c r="U96" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V96" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W96" s="6" t="n">
         <v>0</v>
@@ -5635,13 +4738,13 @@
         <v>0</v>
       </c>
       <c r="Y96" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z96" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA96" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB96" s="6" t="n">
         <v>0</v>
@@ -5655,7 +4758,7 @@
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B97" s="14">
         <f>IF(A97=1,"Safe (Start)",IF(OR(A97=$B$8,A97=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A97,$B$7)=0),"Safe","Standard")))</f>
@@ -5692,7 +4795,7 @@
         <v>10</v>
       </c>
       <c r="K97" s="6" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L97" s="6" t="n">
         <v>0</v>
@@ -5754,7 +4857,7 @@
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B98" s="14">
         <f>IF(A98=1,"Safe (Start)",IF(OR(A98=$B$8,A98=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A98,$B$7)=0),"Safe","Standard")))</f>
@@ -5788,10 +4891,10 @@
         <v/>
       </c>
       <c r="J98" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K98" s="6" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="L98" s="6" t="n">
         <v>0</v>
@@ -5803,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="O98" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P98" s="6" t="n">
         <v>0</v>
@@ -5812,7 +4915,7 @@
         <v>0</v>
       </c>
       <c r="R98" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S98" s="6" t="n">
         <v>0</v>
@@ -5821,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="U98" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V98" s="6" t="n">
         <v>0</v>
@@ -5853,7 +4956,7 @@
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B99" s="14">
         <f>IF(A99=1,"Safe (Start)",IF(OR(A99=$B$8,A99=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A99,$B$7)=0),"Safe","Standard")))</f>
@@ -5887,10 +4990,10 @@
         <v/>
       </c>
       <c r="J99" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K99" s="6" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L99" s="6" t="n">
         <v>0</v>
@@ -5902,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P99" s="6" t="n">
         <v>0</v>
@@ -5952,7 +5055,7 @@
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B100" s="14">
         <f>IF(A100=1,"Safe (Start)",IF(OR(A100=$B$8,A100=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A100,$B$7)=0),"Safe","Standard")))</f>
@@ -5986,10 +5089,10 @@
         <v/>
       </c>
       <c r="J100" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K100" s="6" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L100" s="6" t="n">
         <v>0</v>
@@ -6040,10 +5143,10 @@
         <v>0</v>
       </c>
       <c r="AB100" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC100" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD100" s="6" t="n">
         <v>0</v>
@@ -6051,7 +5154,7 @@
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B101" s="14">
         <f>IF(A101=1,"Safe (Start)",IF(OR(A101=$B$8,A101=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A101,$B$7)=0),"Safe","Standard")))</f>
@@ -6088,7 +5191,7 @@
         <v>10</v>
       </c>
       <c r="K101" s="6" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="L101" s="6" t="n">
         <v>0</v>
@@ -6150,7 +5253,7 @@
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B102" s="14">
         <f>IF(A102=1,"Safe (Start)",IF(OR(A102=$B$8,A102=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A102,$B$7)=0),"Safe","Standard")))</f>
@@ -6187,7 +5290,7 @@
         <v>10</v>
       </c>
       <c r="K102" s="6" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L102" s="6" t="n">
         <v>0</v>
@@ -6205,7 +5308,7 @@
         <v>0</v>
       </c>
       <c r="Q102" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R102" s="6" t="n">
         <v>0</v>
@@ -6249,7 +5352,7 @@
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B103" s="14">
         <f>IF(A103=1,"Safe (Start)",IF(OR(A103=$B$8,A103=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A103,$B$7)=0),"Safe","Standard")))</f>
@@ -6283,10 +5386,10 @@
         <v/>
       </c>
       <c r="J103" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K103" s="6" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L103" s="6" t="n">
         <v>0</v>
@@ -6348,7 +5451,7 @@
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B104" s="14">
         <f>IF(A104=1,"Safe (Start)",IF(OR(A104=$B$8,A104=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A104,$B$7)=0),"Safe","Standard")))</f>
@@ -6385,7 +5488,7 @@
         <v>10</v>
       </c>
       <c r="K104" s="6" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L104" s="6" t="n">
         <v>0</v>
@@ -6439,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="AC104" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD104" s="6" t="n">
         <v>0</v>
@@ -6447,7 +5550,7 @@
     </row>
     <row r="105">
       <c r="A105" s="8" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B105" s="14">
         <f>IF(A105=1,"Safe (Start)",IF(OR(A105=$B$8,A105=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A105,$B$7)=0),"Safe","Standard")))</f>
@@ -6481,10 +5584,10 @@
         <v/>
       </c>
       <c r="J105" s="6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K105" s="6" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="L105" s="6" t="n">
         <v>0</v>
@@ -6496,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="O105" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P105" s="6" t="n">
         <v>0</v>
@@ -6546,7 +5649,7 @@
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B106" s="14">
         <f>IF(A106=1,"Safe (Start)",IF(OR(A106=$B$8,A106=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A106,$B$7)=0),"Safe","Standard")))</f>
@@ -6583,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="K106" s="6" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L106" s="6" t="n">
         <v>0</v>
@@ -6595,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="O106" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P106" s="6" t="n">
         <v>0</v>
@@ -6645,7 +5748,7 @@
     </row>
     <row r="107">
       <c r="A107" s="8" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B107" s="14">
         <f>IF(A107=1,"Safe (Start)",IF(OR(A107=$B$8,A107=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A107,$B$7)=0),"Safe","Standard")))</f>
@@ -6682,7 +5785,7 @@
         <v>10</v>
       </c>
       <c r="K107" s="6" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L107" s="6" t="n">
         <v>0</v>
@@ -6744,7 +5847,7 @@
     </row>
     <row r="108">
       <c r="A108" s="8" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B108" s="14">
         <f>IF(A108=1,"Safe (Start)",IF(OR(A108=$B$8,A108=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A108,$B$7)=0),"Safe","Standard")))</f>
@@ -6778,10 +5881,10 @@
         <v/>
       </c>
       <c r="J108" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K108" s="6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="L108" s="6" t="n">
         <v>0</v>
@@ -6835,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="AC108" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD108" s="6" t="n">
         <v>0</v>
@@ -6843,7 +5946,7 @@
     </row>
     <row r="109">
       <c r="A109" s="8" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B109" s="14">
         <f>IF(A109=1,"Safe (Start)",IF(OR(A109=$B$8,A109=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A109,$B$7)=0),"Safe","Standard")))</f>
@@ -6877,10 +5980,10 @@
         <v/>
       </c>
       <c r="J109" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K109" s="6" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="L109" s="6" t="n">
         <v>0</v>
@@ -6942,7 +6045,7 @@
     </row>
     <row r="110">
       <c r="A110" s="8" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B110" s="14">
         <f>IF(A110=1,"Safe (Start)",IF(OR(A110=$B$8,A110=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A110,$B$7)=0),"Safe","Standard")))</f>
@@ -6979,7 +6082,7 @@
         <v>10</v>
       </c>
       <c r="K110" s="6" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="L110" s="6" t="n">
         <v>0</v>
@@ -6991,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="O110" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P110" s="6" t="n">
         <v>0</v>
@@ -7041,7 +6144,7 @@
     </row>
     <row r="111">
       <c r="A111" s="8" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B111" s="14">
         <f>IF(A111=1,"Safe (Start)",IF(OR(A111=$B$8,A111=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A111,$B$7)=0),"Safe","Standard")))</f>
@@ -7075,10 +6178,10 @@
         <v/>
       </c>
       <c r="J111" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K111" s="6" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L111" s="6" t="n">
         <v>0</v>
@@ -7099,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="R111" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S111" s="6" t="n">
         <v>0</v>
@@ -7108,7 +6211,7 @@
         <v>0</v>
       </c>
       <c r="U111" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V111" s="6" t="n">
         <v>0</v>
@@ -7140,7 +6243,7 @@
     </row>
     <row r="112">
       <c r="A112" s="8" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B112" s="14">
         <f>IF(A112=1,"Safe (Start)",IF(OR(A112=$B$8,A112=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A112,$B$7)=0),"Safe","Standard")))</f>
@@ -7177,7 +6280,7 @@
         <v>10</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L112" s="6" t="n">
         <v>0</v>
@@ -7189,7 +6292,7 @@
         <v>0</v>
       </c>
       <c r="O112" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P112" s="6" t="n">
         <v>0</v>
@@ -7239,7 +6342,7 @@
     </row>
     <row r="113">
       <c r="A113" s="8" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B113" s="14">
         <f>IF(A113=1,"Safe (Start)",IF(OR(A113=$B$8,A113=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A113,$B$7)=0),"Safe","Standard")))</f>
@@ -7273,43 +6376,43 @@
         <v/>
       </c>
       <c r="J113" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K113" s="6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L113" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M113" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N113" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O113" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P113" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q113" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R113" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S113" s="6" t="n">
         <v>0</v>
       </c>
       <c r="T113" s="6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="U113" s="6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="V113" s="6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W113" s="6" t="n">
         <v>0</v>
@@ -7324,10 +6427,10 @@
         <v>0</v>
       </c>
       <c r="AA113" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB113" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC113" s="6" t="n">
         <v>1</v>
@@ -7336,100 +6439,1346 @@
         <v>0</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="B114" s="14">
+        <f>IF(A114=1,"Safe (Start)",IF(OR(A114=$B$8,A114=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A114,$B$7)=0),"Safe","Standard")))</f>
+        <v/>
+      </c>
+      <c r="C114" s="14">
+        <f>MIN(6,MAX(1,ROUNDUP(A114/$B$10,0)))</f>
+        <v/>
+      </c>
+      <c r="D114" s="6">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E114" s="14">
+        <f>MAX(0,$D114-$F114-$G114)</f>
+        <v/>
+      </c>
+      <c r="F114" s="14">
+        <f>IF($B114&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C114&lt;=2,1,IF($C114&lt;=4,2,3)))))</f>
+        <v/>
+      </c>
+      <c r="G114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="15">
+        <f>IF($D114&lt;=0,0,($D114-$F114)/$D114)</f>
+        <v/>
+      </c>
+      <c r="I114" s="15">
+        <f>IF($D114-$F114&lt;=0,0,$E114/($D114-$F114))</f>
+        <v/>
+      </c>
+      <c r="J114" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K114" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="L114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD114" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="A115" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="B115" s="14">
+        <f>IF(A115=1,"Safe (Start)",IF(OR(A115=$B$8,A115=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A115,$B$7)=0),"Safe","Standard")))</f>
+        <v/>
+      </c>
+      <c r="C115" s="14">
+        <f>MIN(6,MAX(1,ROUNDUP(A115/$B$10,0)))</f>
+        <v/>
+      </c>
+      <c r="D115" s="6">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E115" s="14">
+        <f>MAX(0,$D115-$F115-$G115)</f>
+        <v/>
+      </c>
+      <c r="F115" s="14">
+        <f>IF($B115&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C115&lt;=2,1,IF($C115&lt;=4,2,3)))))</f>
+        <v/>
+      </c>
+      <c r="G115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="15">
+        <f>IF($D115&lt;=0,0,($D115-$F115)/$D115)</f>
+        <v/>
+      </c>
+      <c r="I115" s="15">
+        <f>IF($D115-$F115&lt;=0,0,$E115/($D115-$F115))</f>
+        <v/>
+      </c>
+      <c r="J115" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K115" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="L115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD115" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B116" s="14">
+        <f>IF(A116=1,"Safe (Start)",IF(OR(A116=$B$8,A116=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A116,$B$7)=0),"Safe","Standard")))</f>
+        <v/>
+      </c>
+      <c r="C116" s="14">
+        <f>MIN(6,MAX(1,ROUNDUP(A116/$B$10,0)))</f>
+        <v/>
+      </c>
+      <c r="D116" s="6">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E116" s="14">
+        <f>MAX(0,$D116-$F116-$G116)</f>
+        <v/>
+      </c>
+      <c r="F116" s="14">
+        <f>IF($B116&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C116&lt;=2,1,IF($C116&lt;=4,2,3)))))</f>
+        <v/>
+      </c>
+      <c r="G116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="15">
+        <f>IF($D116&lt;=0,0,($D116-$F116)/$D116)</f>
+        <v/>
+      </c>
+      <c r="I116" s="15">
+        <f>IF($D116-$F116&lt;=0,0,$E116/($D116-$F116))</f>
+        <v/>
+      </c>
+      <c r="J116" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K116" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="L116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="B117" s="14">
+        <f>IF(A117=1,"Safe (Start)",IF(OR(A117=$B$8,A117=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A117,$B$7)=0),"Safe","Standard")))</f>
+        <v/>
+      </c>
+      <c r="C117" s="14">
+        <f>MIN(6,MAX(1,ROUNDUP(A117/$B$10,0)))</f>
+        <v/>
+      </c>
+      <c r="D117" s="6">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E117" s="14">
+        <f>MAX(0,$D117-$F117-$G117)</f>
+        <v/>
+      </c>
+      <c r="F117" s="14">
+        <f>IF($B117&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C117&lt;=2,1,IF($C117&lt;=4,2,3)))))</f>
+        <v/>
+      </c>
+      <c r="G117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="15">
+        <f>IF($D117&lt;=0,0,($D117-$F117)/$D117)</f>
+        <v/>
+      </c>
+      <c r="I117" s="15">
+        <f>IF($D117-$F117&lt;=0,0,$E117/($D117-$F117))</f>
+        <v/>
+      </c>
+      <c r="J117" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K117" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="L117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD117" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="B118" s="14">
+        <f>IF(A118=1,"Safe (Start)",IF(OR(A118=$B$8,A118=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A118,$B$7)=0),"Safe","Standard")))</f>
+        <v/>
+      </c>
+      <c r="C118" s="14">
+        <f>MIN(6,MAX(1,ROUNDUP(A118/$B$10,0)))</f>
+        <v/>
+      </c>
+      <c r="D118" s="6">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E118" s="14">
+        <f>MAX(0,$D118-$F118-$G118)</f>
+        <v/>
+      </c>
+      <c r="F118" s="14">
+        <f>IF($B118&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C118&lt;=2,1,IF($C118&lt;=4,2,3)))))</f>
+        <v/>
+      </c>
+      <c r="G118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="15">
+        <f>IF($D118&lt;=0,0,($D118-$F118)/$D118)</f>
+        <v/>
+      </c>
+      <c r="I118" s="15">
+        <f>IF($D118-$F118&lt;=0,0,$E118/($D118-$F118))</f>
+        <v/>
+      </c>
+      <c r="J118" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K118" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="L118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD118" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="B119" s="14">
+        <f>IF(A119=1,"Safe (Start)",IF(OR(A119=$B$8,A119=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A119,$B$7)=0),"Safe","Standard")))</f>
+        <v/>
+      </c>
+      <c r="C119" s="14">
+        <f>MIN(6,MAX(1,ROUNDUP(A119/$B$10,0)))</f>
+        <v/>
+      </c>
+      <c r="D119" s="6">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E119" s="14">
+        <f>MAX(0,$D119-$F119-$G119)</f>
+        <v/>
+      </c>
+      <c r="F119" s="14">
+        <f>IF($B119&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C119&lt;=2,1,IF($C119&lt;=4,2,3)))))</f>
+        <v/>
+      </c>
+      <c r="G119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="15">
+        <f>IF($D119&lt;=0,0,($D119-$F119)/$D119)</f>
+        <v/>
+      </c>
+      <c r="I119" s="15">
+        <f>IF($D119-$F119&lt;=0,0,$E119/($D119-$F119))</f>
+        <v/>
+      </c>
+      <c r="J119" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K119" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="L119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD119" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="B120" s="14">
+        <f>IF(A120=1,"Safe (Start)",IF(OR(A120=$B$8,A120=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A120,$B$7)=0),"Safe","Standard")))</f>
+        <v/>
+      </c>
+      <c r="C120" s="14">
+        <f>MIN(6,MAX(1,ROUNDUP(A120/$B$10,0)))</f>
+        <v/>
+      </c>
+      <c r="D120" s="6">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E120" s="14">
+        <f>MAX(0,$D120-$F120-$G120)</f>
+        <v/>
+      </c>
+      <c r="F120" s="14">
+        <f>IF($B120&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C120&lt;=2,1,IF($C120&lt;=4,2,3)))))</f>
+        <v/>
+      </c>
+      <c r="G120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="15">
+        <f>IF($D120&lt;=0,0,($D120-$F120)/$D120)</f>
+        <v/>
+      </c>
+      <c r="I120" s="15">
+        <f>IF($D120-$F120&lt;=0,0,$E120/($D120-$F120))</f>
+        <v/>
+      </c>
+      <c r="J120" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K120" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="L120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD120" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="B121" s="14">
+        <f>IF(A121=1,"Safe (Start)",IF(OR(A121=$B$8,A121=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A121,$B$7)=0),"Safe","Standard")))</f>
+        <v/>
+      </c>
+      <c r="C121" s="14">
+        <f>MIN(6,MAX(1,ROUNDUP(A121/$B$10,0)))</f>
+        <v/>
+      </c>
+      <c r="D121" s="6">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E121" s="14">
+        <f>MAX(0,$D121-$F121-$G121)</f>
+        <v/>
+      </c>
+      <c r="F121" s="14">
+        <f>IF($B121&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C121&lt;=2,1,IF($C121&lt;=4,2,3)))))</f>
+        <v/>
+      </c>
+      <c r="G121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="15">
+        <f>IF($D121&lt;=0,0,($D121-$F121)/$D121)</f>
+        <v/>
+      </c>
+      <c r="I121" s="15">
+        <f>IF($D121-$F121&lt;=0,0,$E121/($D121-$F121))</f>
+        <v/>
+      </c>
+      <c r="J121" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K121" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="L121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD121" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="B122" s="14">
+        <f>IF(A122=1,"Safe (Start)",IF(OR(A122=$B$8,A122=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A122,$B$7)=0),"Safe","Standard")))</f>
+        <v/>
+      </c>
+      <c r="C122" s="14">
+        <f>MIN(6,MAX(1,ROUNDUP(A122/$B$10,0)))</f>
+        <v/>
+      </c>
+      <c r="D122" s="6">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E122" s="14">
+        <f>MAX(0,$D122-$F122-$G122)</f>
+        <v/>
+      </c>
+      <c r="F122" s="14">
+        <f>IF($B122&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C122&lt;=2,1,IF($C122&lt;=4,2,3)))))</f>
+        <v/>
+      </c>
+      <c r="G122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="15">
+        <f>IF($D122&lt;=0,0,($D122-$F122)/$D122)</f>
+        <v/>
+      </c>
+      <c r="I122" s="15">
+        <f>IF($D122-$F122&lt;=0,0,$E122/($D122-$F122))</f>
+        <v/>
+      </c>
+      <c r="J122" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K122" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="L122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD122" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="B123" s="14">
+        <f>IF(A123=1,"Safe (Start)",IF(OR(A123=$B$8,A123=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A123,$B$7)=0),"Safe","Standard")))</f>
+        <v/>
+      </c>
+      <c r="C123" s="14">
+        <f>MIN(6,MAX(1,ROUNDUP(A123/$B$10,0)))</f>
+        <v/>
+      </c>
+      <c r="D123" s="6">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E123" s="14">
+        <f>MAX(0,$D123-$F123-$G123)</f>
+        <v/>
+      </c>
+      <c r="F123" s="14">
+        <f>IF($B123&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C123&lt;=2,1,IF($C123&lt;=4,2,3)))))</f>
+        <v/>
+      </c>
+      <c r="G123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="15">
+        <f>IF($D123&lt;=0,0,($D123-$F123)/$D123)</f>
+        <v/>
+      </c>
+      <c r="I123" s="15">
+        <f>IF($D123-$F123&lt;=0,0,$E123/($D123-$F123))</f>
+        <v/>
+      </c>
+      <c r="J123" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K123" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="L123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD123" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="B124" s="14">
+        <f>IF(A124=1,"Safe (Start)",IF(OR(A124=$B$8,A124=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A124,$B$7)=0),"Safe","Standard")))</f>
+        <v/>
+      </c>
+      <c r="C124" s="14">
+        <f>MIN(6,MAX(1,ROUNDUP(A124/$B$10,0)))</f>
+        <v/>
+      </c>
+      <c r="D124" s="6">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E124" s="14">
+        <f>MAX(0,$D124-$F124-$G124)</f>
+        <v/>
+      </c>
+      <c r="F124" s="14">
+        <f>IF($B124&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C124&lt;=2,1,IF($C124&lt;=4,2,3)))))</f>
+        <v/>
+      </c>
+      <c r="G124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="15">
+        <f>IF($D124&lt;=0,0,($D124-$F124)/$D124)</f>
+        <v/>
+      </c>
+      <c r="I124" s="15">
+        <f>IF($D124-$F124&lt;=0,0,$E124/($D124-$F124))</f>
+        <v/>
+      </c>
+      <c r="J124" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K124" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="L124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD124" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="B125" s="14">
+        <f>IF(A125=1,"Safe (Start)",IF(OR(A125=$B$8,A125=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A125,$B$7)=0),"Safe","Standard")))</f>
+        <v/>
+      </c>
+      <c r="C125" s="14">
+        <f>MIN(6,MAX(1,ROUNDUP(A125/$B$10,0)))</f>
+        <v/>
+      </c>
+      <c r="D125" s="6">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E125" s="14">
+        <f>MAX(0,$D125-$F125-$G125)</f>
+        <v/>
+      </c>
+      <c r="F125" s="14">
+        <f>IF($B125&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C125&lt;=2,1,IF($C125&lt;=4,2,3)))))</f>
+        <v/>
+      </c>
+      <c r="G125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="15">
+        <f>IF($D125&lt;=0,0,($D125-$F125)/$D125)</f>
+        <v/>
+      </c>
+      <c r="I125" s="15">
+        <f>IF($D125-$F125&lt;=0,0,$E125/($D125-$F125))</f>
+        <v/>
+      </c>
+      <c r="J125" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K125" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="L125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="B126" s="14">
+        <f>IF(A126=1,"Safe (Start)",IF(OR(A126=$B$8,A126=$B$9),"Milestone",IF(AND($B$7&gt;0,MOD(A126,$B$7)=0),"Safe","Standard")))</f>
+        <v/>
+      </c>
+      <c r="C126" s="14">
+        <f>MIN(6,MAX(1,ROUNDUP(A126/$B$10,0)))</f>
+        <v/>
+      </c>
+      <c r="D126" s="6">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E126" s="14">
+        <f>MAX(0,$D126-$F126-$G126)</f>
+        <v/>
+      </c>
+      <c r="F126" s="14">
+        <f>IF($B126&lt;&gt;"Standard",0,MIN(3,MAX($B$6,IF($C126&lt;=2,1,IF($C126&lt;=4,2,3)))))</f>
+        <v/>
+      </c>
+      <c r="G126" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="15">
+        <f>IF($D126&lt;=0,0,($D126-$F126)/$D126)</f>
+        <v/>
+      </c>
+      <c r="I126" s="15">
+        <f>IF($D126-$F126&lt;=0,0,$E126/($D126-$F126))</f>
+        <v/>
+      </c>
+      <c r="J126" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K126" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="L126" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N126" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O126" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P126" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q126" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R126" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S126" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="U126" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="V126" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="W126" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB126" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC126" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD126" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>SIM PART  —  spilled by ECOGAINS_TOF, do not type here</t>
         </is>
       </c>
-      <c r="B115" s="3" t="n"/>
-      <c r="C115" s="3" t="n"/>
-      <c r="D115" s="3" t="n"/>
-      <c r="E115" s="3" t="n"/>
-      <c r="F115" s="3" t="n"/>
-      <c r="G115" s="3" t="n"/>
-      <c r="H115" s="3" t="n"/>
-      <c r="I115" s="3" t="n"/>
-      <c r="J115" s="3" t="n"/>
-      <c r="K115" s="3" t="n"/>
-      <c r="L115" s="3" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="7" t="inlineStr">
+      <c r="B128" s="3" t="n"/>
+      <c r="C128" s="3" t="n"/>
+      <c r="D128" s="3" t="n"/>
+      <c r="E128" s="3" t="n"/>
+      <c r="F128" s="3" t="n"/>
+      <c r="G128" s="3" t="n"/>
+      <c r="H128" s="3" t="n"/>
+      <c r="I128" s="3" t="n"/>
+      <c r="J128" s="3" t="n"/>
+      <c r="K128" s="3" t="n"/>
+      <c r="L128" s="3" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
         <is>
           <t>Everything below is written by the engine. The yellow cells above are the only inputs.</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="7" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
         <is>
           <t>Payer picks which flag the three blocks are computed for. The trailing sim_refresh!$A$1 in each formula is the refresh nonce: Google only re-runs a custom function when its ARGUMENTS change, so without it an edit to the ladder above would leave a stale spill sitting here.</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="16" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="16" t="inlineStr">
         <is>
           <t>Payer</t>
         </is>
       </c>
-      <c r="B118" s="6" t="inlineStr">
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>NONPAYER</t>
         </is>
       </c>
-      <c r="C118" s="7" t="inlineStr">
+      <c r="C131" s="7" t="inlineStr">
         <is>
           <t>NONPAYER or PAYER.</t>
         </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>RUN ECONOMICS</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="n"/>
-      <c r="C120" s="3" t="n"/>
-      <c r="D120" s="3" t="n"/>
-      <c r="E120" s="3" t="n"/>
-      <c r="F120" s="3" t="n"/>
-      <c r="G120" s="3" t="n"/>
-      <c r="H120" s="3" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="7" t="inlineStr">
-        <is>
-          <t>One row per segment: runs taken in the 33-day window, the chance a run pays anything at all, the coins spent on continues per run and across the window, and the ticket flow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="7" t="inlineStr">
-        <is>
-          <t>Runs are NOT a config number. The engine banks whatever ToF_Ticket the rest of the calendar paid that day and spends it, up to Runs per Active Day, carrying leftovers forward.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="7" t="inlineStr">
-        <is>
-          <t>MAX spills BLANK in the window columns: data_seg_beh has no MAX row, so there are no activity rates to price reach with. Its per-run columns are the point of it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="5">
-        <f>ECOGAINS_TOF($B$118, "RUN", sim_refresh!$A$1)</f>
-        <v/>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>BANKED REWARD PER RUN</t>
+          <t>RUN ECONOMICS</t>
         </is>
       </c>
       <c r="B133" s="3" t="n"/>
@@ -7443,76 +7792,117 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
+          <t>One row per segment: runs taken in the 33-day window, the chance a run pays anything at all, the coins spent on continues per run and across the window, and the ticket flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>Runs are NOT a config number. The engine banks whatever ToF_Ticket the rest of the calendar paid that day and spends it, up to Runs per Active Day, carrying leftovers forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>MAX spills BLANK in the window columns: data_seg_beh has no MAX row, so there are no activity rates to price reach with. Its per-run columns are the point of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5">
+        <f>ECOGAINS_TOF($B$131, "RUN", sim_refresh!$A$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>BANKED REWARD PER RUN</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="n"/>
+      <c r="C146" s="3" t="n"/>
+      <c r="D146" s="3" t="n"/>
+      <c r="E146" s="3" t="n"/>
+      <c r="F146" s="3" t="n"/>
+      <c r="G146" s="3" t="n"/>
+      <c r="H146" s="3" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
           <t>What one run actually banks, per resource, already multiplied by the chance of banking it. A run that meets a Pig and stops pays NOTHING, so these are well below the ladder face value.</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="5">
-        <f>ECOGAINS_TOF($B$118, "REWARD", sim_refresh!$A$1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="5">
+        <f>ECOGAINS_TOF($B$131, "REWARD", sim_refresh!$A$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>GAIN VS SPEND</t>
         </is>
       </c>
-      <c r="B163" s="3" t="n"/>
-      <c r="C163" s="3" t="n"/>
-      <c r="D163" s="3" t="n"/>
-      <c r="E163" s="3" t="n"/>
-      <c r="F163" s="3" t="n"/>
-      <c r="G163" s="3" t="n"/>
-      <c r="H163" s="3" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="7" t="inlineStr">
+      <c r="B176" s="3" t="n"/>
+      <c r="C176" s="3" t="n"/>
+      <c r="D176" s="3" t="n"/>
+      <c r="E176" s="3" t="n"/>
+      <c r="F176" s="3" t="n"/>
+      <c r="G176" s="3" t="n"/>
+      <c r="H176" s="3" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="7" t="inlineStr">
         <is>
           <t>Per stage and per segment: gain (raw) is what the ladder holds if you get there; gain (exp) prices in the chance of getting there AND banking it; spend is the expected coins paid for continues along the way; net is exp minus spend.</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="7" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="7" t="inlineStr">
         <is>
           <t>Net is in COINS, not a percentage. The ratio version reached +53,190% at stage 60 and no chart survives that -- the crossover point is the thing this block exists to show.</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="7" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr">
         <is>
           <t>Rows past a segment cash-out stage are BLANK, not zero: that player stops before them, so a flat negative net across stages nobody plays would read as a loss that never happens.</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="7" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="7" t="inlineStr">
         <is>
           <t>Values come from item_vals, so SPT and boosters count -- coins alone are a small part of what this event pays.</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="5">
-        <f>ECOGAINS_TOF($B$118, "GAINSPEND", sim_refresh!$A$1)</f>
+    <row r="181">
+      <c r="A181" s="5">
+        <f>ECOGAINS_TOF($B$131, "GAINSPEND", sim_refresh!$A$1)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A54:AD113">
+  <conditionalFormatting sqref="A67:AD126">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$F54=0</formula>
+      <formula>$F67=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F54:F113">
+  <conditionalFormatting sqref="F67:F126">
     <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="1">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J54:AD113">
+  <conditionalFormatting sqref="J67:AD126">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="2">
       <formula>0</formula>
     </cfRule>
